--- a/ingest/uqn-fix-2026-09-25/review/قائمة-قرارات-حقن-أم-القرى.xlsx
+++ b/ingest/uqn-fix-2026-09-25/review/قائمة-قرارات-حقن-أم-القرى.xlsx
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -882,6 +882,74 @@
       <c r="C10" s="11" t="inlineStr">
         <is>
           <t>آخر main 4e2bf19 (#781): وثائق HKM-028 فقط؛ مجلد ingest/uqn-fix-2026-09-25 بلا تغيير</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>إحلال تنظيم المؤسسة العامة للري (قرار 43) — OP-97c8bc9be4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>عولج بمهمة HKM-026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>التنظيم الجديد طُبّق في حكيم بمهمة HKM-026 (قرار مجلس الوزراء 43، نافذ من 2025-07-18 = النشر 1447-01-23)، والقديم «مستبدل» — لا يُعتمد من الطابور تفاديًا لسجل مكرر</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>إحلال تنظيم الطيران المدني (قرار 807) — OP-f394a79082</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>عولج بمهمة HKM-028</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>التنظيم الجديد طُبّق في حكيم بمهمة HKM-028 (build_hkm028_new_editions.ts): المادة الخامسة عشرة «ويعمل به من تاريخ نشره» = 1446-11-25 (2025-05-23)، والقديم «مستبدل» — لا يُعتمد من الطابور تفاديًا لسجل مكرر</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>مكتب التحرير (HKM-023): الكتابة مفعّلة بأمر المالك 18/10 03:22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>فجوة تنسيق</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>المكتب يقرأ effective_from من uqn_fix.amendment_op (الافتراض) ولا يقرأ effective_corrections.jsonl؛ الاعتماد من المكتب يتجاوز التصحيح — يلزم عرض التاريخ المعاد فيه أو الاعتماد عبر import_review</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ما تعذّر بعد التنسيق</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10 عمليات في 9 مجموعات + 2 مشروطة</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>كان 12؛ عمليتا الري والطيران حُسمتا من عمل HKM-026/HKM-028</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5680,12 @@
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>—  (تغيّر في 1)</t>
+          <t>1447-01-23 (من التنظيم الجديد)</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>إحلال: تاريخ السريان في المادة الختامية للتنظيم/النظام الجديد، ونصه «بالصيغة المرافقة» لم يُنشر في صفحة الأداة ولم يُقرأ</t>
+          <t>التنظيم الجديد طُبّق في حكيم بمهمة HKM-026 (قرار مجلس الوزراء 43، نافذ من 2025-07-18 = النشر 1447-01-23)، والقديم «مستبدل» — لا يُعتمد من الطابور تفاديًا لسجل مكرر</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -5627,12 +5695,12 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>فيه عمليات «مراجعة دقيقة»؛ تاريخ السريان تعذّر/مشروط</t>
+          <t>معالج بمهمة أخرى</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>أجّل الحقن: اقرأ نص التنظيم/النظام المرتبط أولًا (انظر ورقة «تعذّر»)</t>
+          <t>لا تعتمد: عولج في الإنتاج بـ HKM-026 — سجّله «مرفوض» تفاديًا للتكرار</t>
         </is>
       </c>
       <c r="L80" s="8" t="inlineStr"/>
@@ -5671,12 +5739,12 @@
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>—  (تغيّر في 1)</t>
+          <t>1446-11-25 (من التنظيم الجديد)</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>إحلال: تاريخ السريان في المادة الختامية للتنظيم/النظام الجديد، ونصه «بالصيغة المرافقة» لم يُنشر في صفحة الأداة ولم يُقرأ</t>
+          <t>التنظيم الجديد طُبّق في حكيم بمهمة HKM-028 (build_hkm028_new_editions.ts): المادة الخامسة عشرة «ويعمل به من تاريخ نشره» = 1446-11-25 (2025-05-23)، والقديم «مستبدل» — لا يُعتمد من الطابور تفاديًا لسجل مكرر</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -5686,12 +5754,12 @@
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>فيه عمليات «مراجعة دقيقة»؛ تاريخ السريان تعذّر/مشروط</t>
+          <t>معالج بمهمة أخرى</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
-          <t>أجّل الحقن: اقرأ نص التنظيم/النظام المرتبط أولًا (انظر ورقة «تعذّر»)</t>
+          <t>لا تعتمد: عولج في الإنتاج بـ HKM-028 — سجّله «مرفوض» تفاديًا للتكرار</t>
         </is>
       </c>
       <c r="L81" s="8" t="inlineStr"/>
